--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>订单类型</t>
   </si>
@@ -37,9 +37,18 @@
     <t>对账状态</t>
   </si>
   <si>
+    <t>支付状态</t>
+  </si>
+  <si>
+    <t>核算状态</t>
+  </si>
+  <si>
     <t>物流渠道</t>
   </si>
   <si>
+    <t>物流运单号</t>
+  </si>
+  <si>
     <t>物流跟踪单号</t>
   </si>
   <si>
@@ -49,6 +58,9 @@
     <t>实重</t>
   </si>
   <si>
+    <t>体积</t>
+  </si>
+  <si>
     <t>体积重</t>
   </si>
   <si>
@@ -58,16 +70,28 @@
     <t>预估运费</t>
   </si>
   <si>
+    <t>预估关税费用</t>
+  </si>
+  <si>
+    <t>预估可抵扣税金</t>
+  </si>
+  <si>
+    <t>预估其他费用</t>
+  </si>
+  <si>
     <t>计费重[物流商]</t>
   </si>
   <si>
-    <t>实际运费[物流商]</t>
-  </si>
-  <si>
-    <t>实际报关费</t>
-  </si>
-  <si>
-    <t>实际其他费用</t>
+    <t>实际运费[总]</t>
+  </si>
+  <si>
+    <t>实际关税费用[总]</t>
+  </si>
+  <si>
+    <t>实际可抵扣税金[总]</t>
+  </si>
+  <si>
+    <t>实际其他费用[总]</t>
   </si>
   <si>
     <t>运费差异</t>
@@ -79,9 +103,6 @@
     <t>店铺/客户</t>
   </si>
   <si>
-    <t>店铺负责人</t>
-  </si>
-  <si>
     <t>平台单号</t>
   </si>
   <si>
@@ -100,6 +121,15 @@
     <t>发货时间</t>
   </si>
   <si>
+    <t>计费规则</t>
+  </si>
+  <si>
+    <t>账单确认时间</t>
+  </si>
+  <si>
+    <t>付款/退款时间</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -109,9 +139,18 @@
     <t>{.reconciliationStatusName}</t>
   </si>
   <si>
+    <t>{.payStatusName}</t>
+  </si>
+  <si>
+    <t>{.checkStatusName}</t>
+  </si>
+  <si>
     <t>{.channelName}</t>
   </si>
   <si>
+    <t>{.transportNo}</t>
+  </si>
+  <si>
     <t>{.trackNo}</t>
   </si>
   <si>
@@ -121,6 +160,9 @@
     <t>{.actualWeight}</t>
   </si>
   <si>
+    <t>{.volume}</t>
+  </si>
+  <si>
     <t>{.volumeWeight}</t>
   </si>
   <si>
@@ -130,6 +172,15 @@
     <t>{.estimatedShippingCost}</t>
   </si>
   <si>
+    <t>{.estimatedDeclareCost}</t>
+  </si>
+  <si>
+    <t>{.estimatedDeductibleTax}</t>
+  </si>
+  <si>
+    <t>{.estimatedOtherCost}</t>
+  </si>
+  <si>
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
@@ -139,6 +190,9 @@
     <t>{.actualDeclareCost}</t>
   </si>
   <si>
+    <t>{.actualDeductibleTax}</t>
+  </si>
+  <si>
     <t>{.actualOtherCost}</t>
   </si>
   <si>
@@ -151,9 +205,6 @@
     <t>{.customerName}</t>
   </si>
   <si>
-    <t>{.shopChargeName}</t>
-  </si>
-  <si>
     <t>{.platformCode}</t>
   </si>
   <si>
@@ -170,6 +221,15 @@
   </si>
   <si>
     <t>{.deliveryTime}</t>
+  </si>
+  <si>
+    <t>{.feeRuleName}</t>
+  </si>
+  <si>
+    <t>{.confirmTime}</t>
+  </si>
+  <si>
+    <t>{.payTime}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1103,31 +1163,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
     <col min="2" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="13.625" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="16.375" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="13" width="20.75" customWidth="1"/>
-    <col min="14" max="14" width="16.75" customWidth="1"/>
-    <col min="15" max="15" width="16.5" customWidth="1"/>
-    <col min="16" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="18.25" customWidth="1"/>
-    <col min="19" max="19" width="15.75" customWidth="1"/>
-    <col min="20" max="20" width="13.875" customWidth="1"/>
-    <col min="21" max="21" width="13.75" customWidth="1"/>
-    <col min="22" max="23" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="4" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="11" width="16.375" customWidth="1"/>
+    <col min="12" max="12" width="12.375" customWidth="1"/>
+    <col min="13" max="13" width="14.25" customWidth="1"/>
+    <col min="14" max="14" width="21.625" customWidth="1"/>
+    <col min="15" max="15" width="18.375" customWidth="1"/>
+    <col min="16" max="17" width="17.125" customWidth="1"/>
+    <col min="18" max="21" width="20.75" customWidth="1"/>
+    <col min="22" max="22" width="16.75" customWidth="1"/>
+    <col min="23" max="23" width="16.5" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="18.25" customWidth="1"/>
+    <col min="26" max="26" width="15.75" customWidth="1"/>
+    <col min="27" max="27" width="13.875" customWidth="1"/>
+    <col min="28" max="28" width="13.75" customWidth="1"/>
+    <col min="29" max="30" width="13.125" customWidth="1"/>
+    <col min="31" max="31" width="8.875" customWidth="1"/>
+    <col min="32" max="32" width="12.875" customWidth="1"/>
+    <col min="33" max="33" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1200,79 +1267,139 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:34">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="Q2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="R2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="W2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
@@ -169,34 +169,34 @@
     <t>{.billingWeight}</t>
   </si>
   <si>
-    <t>{.estimatedShippingCost}</t>
-  </si>
-  <si>
-    <t>{.estimatedDeclareCost}</t>
-  </si>
-  <si>
-    <t>{.estimatedDeductibleTax}</t>
-  </si>
-  <si>
-    <t>{.estimatedOtherCost}</t>
+    <t>{.estimatedShippingCostStr}</t>
+  </si>
+  <si>
+    <t>{.estimatedDeclareCostStr}</t>
+  </si>
+  <si>
+    <t>{.estimatedDeductibleTaxStr}</t>
+  </si>
+  <si>
+    <t>{.estimatedOtherCostStr}</t>
   </si>
   <si>
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
-    <t>{.actualShippingCost}</t>
-  </si>
-  <si>
-    <t>{.actualDeclareCost}</t>
-  </si>
-  <si>
-    <t>{.actualDeductibleTax}</t>
-  </si>
-  <si>
-    <t>{.actualOtherCost}</t>
-  </si>
-  <si>
-    <t>{.diffShippingCost}</t>
+    <t>{.actualShippingCostStr}</t>
+  </si>
+  <si>
+    <t>{.actualDeclareCostStr}</t>
+  </si>
+  <si>
+    <t>{.actualDeductibleTaxStr}</t>
+  </si>
+  <si>
+    <t>{.actualOtherCostStr}</t>
+  </si>
+  <si>
+    <t>{.diffShippingCostStr}</t>
   </si>
   <si>
     <t>{.salesPlatform}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>订单类型</t>
   </si>
@@ -43,6 +43,9 @@
     <t>核算状态</t>
   </si>
   <si>
+    <t>物流商</t>
+  </si>
+  <si>
     <t>物流渠道</t>
   </si>
   <si>
@@ -143,6 +146,9 @@
   </si>
   <si>
     <t>{.checkStatusName}</t>
+  </si>
+  <si>
+    <t>{.logisticsSupplierName}</t>
   </si>
   <si>
     <t>{.channelName}</t>
@@ -1163,38 +1169,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
     <col min="2" max="2" width="14.25" customWidth="1"/>
     <col min="3" max="3" width="17.25" customWidth="1"/>
-    <col min="4" max="5" width="14.875" customWidth="1"/>
-    <col min="6" max="6" width="15.625" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13.25" customWidth="1"/>
-    <col min="10" max="11" width="16.375" customWidth="1"/>
-    <col min="12" max="12" width="12.375" customWidth="1"/>
-    <col min="13" max="13" width="14.25" customWidth="1"/>
-    <col min="14" max="14" width="21.625" customWidth="1"/>
-    <col min="15" max="15" width="18.375" customWidth="1"/>
-    <col min="16" max="17" width="17.125" customWidth="1"/>
-    <col min="18" max="21" width="20.75" customWidth="1"/>
-    <col min="22" max="22" width="16.75" customWidth="1"/>
-    <col min="23" max="23" width="16.5" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="18.25" customWidth="1"/>
-    <col min="26" max="26" width="15.75" customWidth="1"/>
-    <col min="27" max="27" width="13.875" customWidth="1"/>
-    <col min="28" max="28" width="13.75" customWidth="1"/>
-    <col min="29" max="30" width="13.125" customWidth="1"/>
-    <col min="31" max="31" width="8.875" customWidth="1"/>
-    <col min="32" max="32" width="12.875" customWidth="1"/>
-    <col min="33" max="33" width="14" customWidth="1"/>
+    <col min="4" max="6" width="14.875" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="13.625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="13.25" customWidth="1"/>
+    <col min="11" max="12" width="16.375" customWidth="1"/>
+    <col min="13" max="13" width="12.375" customWidth="1"/>
+    <col min="14" max="14" width="14.25" customWidth="1"/>
+    <col min="15" max="15" width="21.625" customWidth="1"/>
+    <col min="16" max="16" width="18.375" customWidth="1"/>
+    <col min="17" max="18" width="17.125" customWidth="1"/>
+    <col min="19" max="22" width="20.75" customWidth="1"/>
+    <col min="23" max="23" width="16.75" customWidth="1"/>
+    <col min="24" max="24" width="16.5" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="18.25" customWidth="1"/>
+    <col min="27" max="27" width="15.75" customWidth="1"/>
+    <col min="28" max="28" width="13.875" customWidth="1"/>
+    <col min="29" max="29" width="13.75" customWidth="1"/>
+    <col min="30" max="31" width="13.125" customWidth="1"/>
+    <col min="32" max="32" width="8.875" customWidth="1"/>
+    <col min="33" max="33" width="12.875" customWidth="1"/>
+    <col min="34" max="34" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1297,109 +1303,115 @@
       <c r="AH1" t="s">
         <v>33</v>
       </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:35">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AC2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AH2" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>订单类型</t>
   </si>
@@ -85,6 +83,12 @@
     <t>计费重[物流商]</t>
   </si>
   <si>
+    <t>包装尺寸(物流商)</t>
+  </si>
+  <si>
+    <t>实重(物流商)</t>
+  </si>
+  <si>
     <t>实际运费[总]</t>
   </si>
   <si>
@@ -115,6 +119,9 @@
     <t>出库单号</t>
   </si>
   <si>
+    <t>发货单号</t>
+  </si>
+  <si>
     <t>目的国家</t>
   </si>
   <si>
@@ -139,6 +146,9 @@
     <t>{.orderTypeName}</t>
   </si>
   <si>
+    <t>{.reconciliationMonth}</t>
+  </si>
+  <si>
     <t>{.reconciliationStatusName}</t>
   </si>
   <si>
@@ -190,6 +200,12 @@
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
+    <t>{.thirdPackSize}</t>
+  </si>
+  <si>
+    <t>{.thirdActualWeight}</t>
+  </si>
+  <si>
     <t>{.actualShippingCostStr}</t>
   </si>
   <si>
@@ -218,6 +234,9 @@
   </si>
   <si>
     <t>{.outstockCode}</t>
+  </si>
+  <si>
+    <t>{.soDeliveryCode}</t>
   </si>
   <si>
     <t>{.toCountry}</t>
@@ -1169,38 +1188,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AM2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
-    <col min="2" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
-    <col min="4" max="6" width="14.875" customWidth="1"/>
-    <col min="7" max="7" width="15.625" customWidth="1"/>
-    <col min="8" max="8" width="13.625" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="13.25" customWidth="1"/>
-    <col min="11" max="12" width="16.375" customWidth="1"/>
-    <col min="13" max="13" width="12.375" customWidth="1"/>
-    <col min="14" max="14" width="14.25" customWidth="1"/>
-    <col min="15" max="15" width="21.625" customWidth="1"/>
-    <col min="16" max="16" width="18.375" customWidth="1"/>
-    <col min="17" max="18" width="17.125" customWidth="1"/>
-    <col min="19" max="22" width="20.75" customWidth="1"/>
-    <col min="23" max="23" width="16.75" customWidth="1"/>
-    <col min="24" max="24" width="16.5" customWidth="1"/>
-    <col min="25" max="25" width="16" customWidth="1"/>
-    <col min="26" max="26" width="18.25" customWidth="1"/>
-    <col min="27" max="27" width="15.75" customWidth="1"/>
-    <col min="28" max="28" width="13.875" customWidth="1"/>
-    <col min="29" max="29" width="13.75" customWidth="1"/>
-    <col min="30" max="31" width="13.125" customWidth="1"/>
-    <col min="32" max="32" width="8.875" customWidth="1"/>
-    <col min="33" max="33" width="12.875" customWidth="1"/>
-    <col min="34" max="34" width="14" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="17.25" customWidth="1"/>
+    <col min="5" max="7" width="14.875" customWidth="1"/>
+    <col min="8" max="8" width="15.625" customWidth="1"/>
+    <col min="9" max="9" width="13.625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="13.25" customWidth="1"/>
+    <col min="12" max="13" width="16.375" customWidth="1"/>
+    <col min="14" max="14" width="12.375" customWidth="1"/>
+    <col min="15" max="15" width="14.25" customWidth="1"/>
+    <col min="16" max="16" width="21.625" customWidth="1"/>
+    <col min="17" max="17" width="18.375" customWidth="1"/>
+    <col min="18" max="19" width="17.125" customWidth="1"/>
+    <col min="20" max="20" width="17.875" customWidth="1"/>
+    <col min="21" max="21" width="18.125" customWidth="1"/>
+    <col min="22" max="22" width="14.5" customWidth="1"/>
+    <col min="23" max="25" width="20.75" customWidth="1"/>
+    <col min="26" max="26" width="16.75" customWidth="1"/>
+    <col min="27" max="27" width="16.5" customWidth="1"/>
+    <col min="28" max="28" width="16" customWidth="1"/>
+    <col min="29" max="29" width="18.25" customWidth="1"/>
+    <col min="30" max="30" width="15.75" customWidth="1"/>
+    <col min="31" max="31" width="13.875" customWidth="1"/>
+    <col min="32" max="32" width="16.5" customWidth="1"/>
+    <col min="33" max="33" width="13.75" customWidth="1"/>
+    <col min="34" max="35" width="13.125" customWidth="1"/>
+    <col min="36" max="36" width="8.875" customWidth="1"/>
+    <col min="37" max="37" width="12.875" customWidth="1"/>
+    <col min="38" max="38" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:39">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1208,210 +1232,234 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
+      <c r="AK1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:39">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="S2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="T2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="U2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="V2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="W2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="X2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Y2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Z2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AA2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AB2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AC2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AD2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AE2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AF2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AG2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AH2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AI2" t="s">
-        <v>69</v>
+        <v>72</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1419,28 +1467,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsBillCost.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>订单类型</t>
   </si>
@@ -125,6 +125,18 @@
     <t>目的国家</t>
   </si>
   <si>
+    <t>区域</t>
+  </si>
+  <si>
+    <t>部门</t>
+  </si>
+  <si>
+    <t>军区</t>
+  </si>
+  <si>
+    <t>是否分摊</t>
+  </si>
+  <si>
     <t>下单时间</t>
   </si>
   <si>
@@ -240,6 +252,18 @@
   </si>
   <si>
     <t>{.toCountry}</t>
+  </si>
+  <si>
+    <t>{.regionName}</t>
+  </si>
+  <si>
+    <t>{.deptName}</t>
+  </si>
+  <si>
+    <t>{.partitionName}</t>
+  </si>
+  <si>
+    <t>{.isAllocateRequiredName}</t>
   </si>
   <si>
     <t>{.orderTime}</t>
@@ -1188,7 +1212,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1218,13 +1242,17 @@
     <col min="31" max="31" width="13.875" customWidth="1"/>
     <col min="32" max="32" width="16.5" customWidth="1"/>
     <col min="33" max="33" width="13.75" customWidth="1"/>
-    <col min="34" max="35" width="13.125" customWidth="1"/>
-    <col min="36" max="36" width="8.875" customWidth="1"/>
-    <col min="37" max="37" width="12.875" customWidth="1"/>
-    <col min="38" max="38" width="14" customWidth="1"/>
+    <col min="34" max="34" width="18.5" customWidth="1"/>
+    <col min="35" max="35" width="17.25" customWidth="1"/>
+    <col min="36" max="36" width="19.25" customWidth="1"/>
+    <col min="37" max="37" width="19.875" customWidth="1"/>
+    <col min="38" max="39" width="13.125" customWidth="1"/>
+    <col min="40" max="40" width="8.875" customWidth="1"/>
+    <col min="41" max="41" width="12.875" customWidth="1"/>
+    <col min="42" max="42" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:43">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1342,124 +1370,148 @@
       <c r="AM1" t="s">
         <v>37</v>
       </c>
+      <c r="AN1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:39">
+    <row r="2" spans="1:43">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="R2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="U2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="V2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="W2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="X2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Y2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="Z2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AA2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AB2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AC2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AD2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AE2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AF2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AG2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AH2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AI2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AK2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AM2" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
